--- a/2026_FLAIRS-39/TestResults.xlsx
+++ b/2026_FLAIRS-39/TestResults.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geoff/Documents/MyDocuments/Research/Systems/ShZZaM/TheSoftware/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geoff/Documents/MyDocuments/Research/Systems/ShZZaM/2026_FLAIRS-39/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFCB1E6-EBC4-644C-AB11-55CF37229024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718A4653-C423-E64D-A490-70BA2D78D2BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37220" yWindow="620" windowWidth="33660" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="33660" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
